--- a/backend/planos_unoee/plano_generado.xlsx
+++ b/backend/planos_unoee/plano_generado.xlsx
@@ -649,22 +649,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1095839582</v>
+        <v>1042451609</v>
       </c>
       <c r="F2" t="n">
         <v>153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260927</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20260929</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -700,22 +700,22 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1095839582</v>
+        <v>1042451609</v>
       </c>
       <c r="F3" t="n">
         <v>153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260930</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -751,22 +751,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1095839582</v>
+        <v>1042451609</v>
       </c>
       <c r="F4" t="n">
         <v>153</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J4" t="n">

--- a/backend/planos_unoee/plano_generado.xlsx
+++ b/backend/planos_unoee/plano_generado.xlsx
@@ -649,22 +649,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1042451609</v>
+        <v>1090510864</v>
       </c>
       <c r="F2" t="n">
         <v>153</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20260927</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20260929</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -700,22 +700,22 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1042451609</v>
+        <v>1090510864</v>
       </c>
       <c r="F3" t="n">
         <v>153</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -751,22 +751,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1042451609</v>
+        <v>1090510864</v>
       </c>
       <c r="F4" t="n">
         <v>153</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20261003</t>
+          <t>20261027</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261107</t>
         </is>
       </c>
       <c r="J4" t="n">
